--- a/excel_data/input.xlsx
+++ b/excel_data/input.xlsx
@@ -49,19 +49,19 @@
     <t xml:space="preserve">bis</t>
   </si>
   <si>
-    <t xml:space="preserve">YD</t>
-  </si>
-  <si>
     <t xml:space="preserve">5m</t>
   </si>
   <si>
-    <t xml:space="preserve">YU</t>
+    <t xml:space="preserve">YD</t>
   </si>
   <si>
     <t xml:space="preserve">YR</t>
   </si>
   <si>
     <t xml:space="preserve">YL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YU</t>
   </si>
 </sst>
 </file>
@@ -187,7 +187,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="34">
+  <borders count="26">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -266,8 +266,8 @@
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left style="medium"/>
-      <right style="thin"/>
+      <left/>
+      <right style="medium"/>
       <top style="medium"/>
       <bottom/>
       <diagonal/>
@@ -308,38 +308,10 @@
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="medium"/>
-      <right style="thin"/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
       <left style="thin"/>
       <right style="medium"/>
       <top/>
       <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="medium"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="medium"/>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
@@ -394,36 +366,8 @@
     <border diagonalUp="false" diagonalDown="false">
       <left style="medium"/>
       <right/>
-      <top/>
-      <bottom style="medium"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="medium"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="medium"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="medium"/>
-      <right/>
       <top style="medium"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="medium"/>
-      <top/>
-      <bottom style="medium"/>
       <diagonal/>
     </border>
   </borders>
@@ -452,7 +396,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="48">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -585,27 +529,31 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -617,7 +565,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -625,39 +573,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="25" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="26" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="27" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="28" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="29" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="31" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -665,11 +581,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -760,9 +672,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>168480</xdr:colOff>
+      <xdr:colOff>168120</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>168480</xdr:rowOff>
+      <xdr:rowOff>168120</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -772,7 +684,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="4153680" y="1550160"/>
-          <a:ext cx="142200" cy="142200"/>
+          <a:ext cx="141840" cy="141840"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -1841,13 +1753,13 @@
       <c r="AK12" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="AL12" s="33" t="s">
+      <c r="AL12" s="27" t="s">
         <v>1</v>
       </c>
       <c r="AU12" s="3"/>
       <c r="AV12" s="3"/>
       <c r="AW12" s="3"/>
-      <c r="AX12" s="34"/>
+      <c r="AX12" s="33"/>
       <c r="AY12" s="18"/>
       <c r="AZ12" s="18"/>
       <c r="BA12" s="18"/>
@@ -1897,7 +1809,7 @@
       <c r="C13" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D13" s="35" t="s">
+      <c r="D13" s="34" t="s">
         <v>7</v>
       </c>
       <c r="E13" s="30" t="s">
@@ -1999,13 +1911,13 @@
       <c r="AK13" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="AL13" s="36" t="s">
+      <c r="AL13" s="34" t="s">
         <v>7</v>
       </c>
       <c r="AU13" s="3"/>
       <c r="AV13" s="3"/>
       <c r="AW13" s="3"/>
-      <c r="AX13" s="34"/>
+      <c r="AX13" s="33"/>
       <c r="AY13" s="18"/>
       <c r="AZ13" s="18"/>
       <c r="BA13" s="18"/>
@@ -2055,8 +1967,8 @@
       <c r="C14" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D14" s="37" t="s">
-        <v>9</v>
+      <c r="D14" s="27" t="s">
+        <v>1</v>
       </c>
       <c r="E14" s="30" t="s">
         <v>4</v>
@@ -2157,13 +2069,13 @@
       <c r="AK14" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="AL14" s="38" t="s">
-        <v>9</v>
+      <c r="AL14" s="27" t="s">
+        <v>1</v>
       </c>
       <c r="AU14" s="3"/>
       <c r="AV14" s="3"/>
       <c r="AW14" s="3"/>
-      <c r="AX14" s="34"/>
+      <c r="AX14" s="33"/>
       <c r="AY14" s="18"/>
       <c r="AZ14" s="18"/>
       <c r="BA14" s="18"/>
@@ -2208,13 +2120,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D15" s="35" t="s">
-        <v>11</v>
+      <c r="D15" s="34" t="s">
+        <v>7</v>
       </c>
       <c r="E15" s="30" t="s">
         <v>4</v>
@@ -2315,13 +2227,13 @@
       <c r="AK15" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="AL15" s="36" t="s">
-        <v>11</v>
+      <c r="AL15" s="34" t="s">
+        <v>7</v>
       </c>
       <c r="AU15" s="3"/>
       <c r="AV15" s="3"/>
       <c r="AW15" s="3"/>
-      <c r="AX15" s="34"/>
+      <c r="AX15" s="33"/>
       <c r="AY15" s="18"/>
       <c r="AZ15" s="18"/>
       <c r="BA15" s="18"/>
@@ -2368,8 +2280,8 @@
       <c r="C16" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="D16" s="37" t="s">
-        <v>9</v>
+      <c r="D16" s="27" t="s">
+        <v>1</v>
       </c>
       <c r="E16" s="30" t="s">
         <v>4</v>
@@ -2470,13 +2382,13 @@
       <c r="AK16" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="AL16" s="38" t="s">
-        <v>9</v>
+      <c r="AL16" s="27" t="s">
+        <v>1</v>
       </c>
       <c r="AU16" s="3"/>
       <c r="AV16" s="3"/>
       <c r="AW16" s="3"/>
-      <c r="AX16" s="34"/>
+      <c r="AX16" s="33"/>
       <c r="AY16" s="18"/>
       <c r="AZ16" s="18"/>
       <c r="BA16" s="18"/>
@@ -2523,30 +2435,30 @@
       <c r="C17" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="D17" s="35" t="s">
+      <c r="D17" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="F17" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="G17" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="H17" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="I17" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="J17" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="E17" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="F17" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="G17" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="H17" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="I17" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="J17" s="40" t="s">
+      <c r="K17" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="K17" s="41" t="s">
-        <v>13</v>
-      </c>
       <c r="L17" s="31" t="s">
         <v>5</v>
       </c>
@@ -2559,14 +2471,14 @@
       <c r="O17" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="P17" s="40" t="s">
+      <c r="P17" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q17" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="Q17" s="42" t="s">
-        <v>13</v>
-      </c>
-      <c r="R17" s="43" t="s">
-        <v>9</v>
+      <c r="R17" s="39" t="s">
+        <v>10</v>
       </c>
       <c r="S17" s="30" t="s">
         <v>4</v>
@@ -2583,15 +2495,15 @@
       <c r="W17" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="X17" s="43" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y17" s="42" t="s">
+      <c r="X17" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y17" s="38" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z17" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="Z17" s="41" t="s">
-        <v>13</v>
-      </c>
       <c r="AA17" s="31" t="s">
         <v>5</v>
       </c>
@@ -2604,14 +2516,14 @@
       <c r="AD17" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="AE17" s="40" t="s">
+      <c r="AE17" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="AF17" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="AF17" s="41" t="s">
-        <v>13</v>
-      </c>
-      <c r="AG17" s="44" t="s">
-        <v>9</v>
+      <c r="AG17" s="40" t="s">
+        <v>10</v>
       </c>
       <c r="AH17" s="30" t="s">
         <v>4</v>
@@ -2625,14 +2537,14 @@
       <c r="AK17" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="AL17" s="36" t="s">
-        <v>11</v>
+      <c r="AL17" s="34" t="s">
+        <v>7</v>
       </c>
       <c r="AN17" s="21"/>
       <c r="AU17" s="3"/>
       <c r="AV17" s="3"/>
       <c r="AW17" s="3"/>
-      <c r="AX17" s="34"/>
+      <c r="AX17" s="33"/>
       <c r="AY17" s="18"/>
       <c r="AZ17" s="18"/>
       <c r="BA17" s="18"/>
@@ -2679,8 +2591,8 @@
       <c r="C18" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D18" s="37" t="s">
-        <v>9</v>
+      <c r="D18" s="27" t="s">
+        <v>1</v>
       </c>
       <c r="E18" s="30" t="s">
         <v>4</v>
@@ -2694,8 +2606,8 @@
       <c r="H18" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="I18" s="45" t="s">
-        <v>11</v>
+      <c r="I18" s="41" t="s">
+        <v>13</v>
       </c>
       <c r="J18" s="31" t="s">
         <v>5</v>
@@ -2721,8 +2633,8 @@
       <c r="Q18" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="R18" s="45" t="s">
-        <v>11</v>
+      <c r="R18" s="41" t="s">
+        <v>13</v>
       </c>
       <c r="S18" s="30" t="s">
         <v>4</v>
@@ -2739,8 +2651,8 @@
       <c r="W18" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="X18" s="45" t="s">
-        <v>11</v>
+      <c r="X18" s="41" t="s">
+        <v>13</v>
       </c>
       <c r="Y18" s="31" t="s">
         <v>5</v>
@@ -2766,8 +2678,8 @@
       <c r="AF18" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="AG18" s="45" t="s">
-        <v>11</v>
+      <c r="AG18" s="41" t="s">
+        <v>13</v>
       </c>
       <c r="AH18" s="30" t="s">
         <v>4</v>
@@ -2781,14 +2693,14 @@
       <c r="AK18" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="AL18" s="38" t="s">
-        <v>9</v>
+      <c r="AL18" s="27" t="s">
+        <v>1</v>
       </c>
       <c r="AN18" s="21"/>
       <c r="AU18" s="3"/>
       <c r="AV18" s="3"/>
       <c r="AW18" s="3"/>
-      <c r="AX18" s="34"/>
+      <c r="AX18" s="33"/>
       <c r="AY18" s="18"/>
       <c r="AZ18" s="18"/>
       <c r="BA18" s="18"/>
@@ -2835,8 +2747,8 @@
       <c r="C19" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="D19" s="35" t="s">
-        <v>11</v>
+      <c r="D19" s="34" t="s">
+        <v>7</v>
       </c>
       <c r="E19" s="30" t="s">
         <v>4</v>
@@ -2937,13 +2849,13 @@
       <c r="AK19" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="AL19" s="36" t="s">
-        <v>11</v>
+      <c r="AL19" s="34" t="s">
+        <v>7</v>
       </c>
       <c r="AU19" s="3"/>
       <c r="AV19" s="3"/>
       <c r="AW19" s="3"/>
-      <c r="AX19" s="34"/>
+      <c r="AX19" s="33"/>
       <c r="AY19" s="18"/>
       <c r="AZ19" s="18"/>
       <c r="BA19" s="18"/>
@@ -2990,8 +2902,8 @@
       <c r="C20" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="D20" s="37" t="s">
-        <v>9</v>
+      <c r="D20" s="27" t="s">
+        <v>1</v>
       </c>
       <c r="E20" s="30" t="s">
         <v>4</v>
@@ -3092,13 +3004,13 @@
       <c r="AK20" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="AL20" s="38" t="s">
-        <v>9</v>
+      <c r="AL20" s="27" t="s">
+        <v>1</v>
       </c>
       <c r="AU20" s="3"/>
       <c r="AV20" s="3"/>
       <c r="AW20" s="3"/>
-      <c r="AX20" s="34"/>
+      <c r="AX20" s="33"/>
       <c r="AY20" s="18"/>
       <c r="AZ20" s="18"/>
       <c r="BA20" s="18"/>
@@ -3145,8 +3057,8 @@
       <c r="C21" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="D21" s="35" t="s">
-        <v>11</v>
+      <c r="D21" s="34" t="s">
+        <v>7</v>
       </c>
       <c r="E21" s="30" t="s">
         <v>4</v>
@@ -3247,13 +3159,13 @@
       <c r="AK21" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="AL21" s="36" t="s">
-        <v>11</v>
+      <c r="AL21" s="34" t="s">
+        <v>7</v>
       </c>
       <c r="AU21" s="3"/>
       <c r="AV21" s="3"/>
       <c r="AW21" s="3"/>
-      <c r="AX21" s="34"/>
+      <c r="AX21" s="33"/>
       <c r="AY21" s="18"/>
       <c r="AZ21" s="18"/>
       <c r="BA21" s="18"/>
@@ -3300,8 +3212,8 @@
       <c r="C22" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="D22" s="37" t="s">
-        <v>9</v>
+      <c r="D22" s="27" t="s">
+        <v>1</v>
       </c>
       <c r="E22" s="30" t="s">
         <v>4</v>
@@ -3402,13 +3314,13 @@
       <c r="AK22" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="AL22" s="38" t="s">
-        <v>9</v>
+      <c r="AL22" s="27" t="s">
+        <v>1</v>
       </c>
       <c r="AU22" s="3"/>
       <c r="AV22" s="3"/>
       <c r="AW22" s="3"/>
-      <c r="AX22" s="34"/>
+      <c r="AX22" s="33"/>
       <c r="AY22" s="18"/>
       <c r="AZ22" s="18"/>
       <c r="BA22" s="18"/>
@@ -3455,8 +3367,8 @@
       <c r="C23" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D23" s="35" t="s">
-        <v>11</v>
+      <c r="D23" s="34" t="s">
+        <v>7</v>
       </c>
       <c r="E23" s="30" t="s">
         <v>4</v>
@@ -3557,13 +3469,13 @@
       <c r="AK23" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="AL23" s="36" t="s">
-        <v>11</v>
+      <c r="AL23" s="34" t="s">
+        <v>7</v>
       </c>
       <c r="AU23" s="3"/>
       <c r="AV23" s="3"/>
       <c r="AW23" s="3"/>
-      <c r="AX23" s="34"/>
+      <c r="AX23" s="33"/>
       <c r="AY23" s="18"/>
       <c r="AZ23" s="18"/>
       <c r="BA23" s="18"/>
@@ -3610,8 +3522,8 @@
       <c r="C24" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="D24" s="37" t="s">
-        <v>9</v>
+      <c r="D24" s="27" t="s">
+        <v>1</v>
       </c>
       <c r="E24" s="30" t="s">
         <v>4</v>
@@ -3712,13 +3624,13 @@
       <c r="AK24" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="AL24" s="38" t="s">
-        <v>9</v>
+      <c r="AL24" s="27" t="s">
+        <v>1</v>
       </c>
       <c r="AU24" s="3"/>
       <c r="AV24" s="3"/>
       <c r="AW24" s="3"/>
-      <c r="AX24" s="34"/>
+      <c r="AX24" s="33"/>
       <c r="AY24" s="18"/>
       <c r="AZ24" s="18"/>
       <c r="BA24" s="18"/>
@@ -3765,8 +3677,8 @@
       <c r="C25" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="D25" s="35" t="s">
-        <v>11</v>
+      <c r="D25" s="34" t="s">
+        <v>7</v>
       </c>
       <c r="E25" s="30" t="s">
         <v>4</v>
@@ -3780,8 +3692,8 @@
       <c r="H25" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="I25" s="43" t="s">
-        <v>9</v>
+      <c r="I25" s="39" t="s">
+        <v>10</v>
       </c>
       <c r="J25" s="31" t="s">
         <v>5</v>
@@ -3807,8 +3719,8 @@
       <c r="Q25" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="R25" s="43" t="s">
-        <v>9</v>
+      <c r="R25" s="39" t="s">
+        <v>10</v>
       </c>
       <c r="S25" s="30" t="s">
         <v>4</v>
@@ -3825,8 +3737,8 @@
       <c r="W25" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="X25" s="43" t="s">
-        <v>9</v>
+      <c r="X25" s="39" t="s">
+        <v>10</v>
       </c>
       <c r="Y25" s="31" t="s">
         <v>5</v>
@@ -3852,8 +3764,8 @@
       <c r="AF25" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="AG25" s="43" t="s">
-        <v>9</v>
+      <c r="AG25" s="39" t="s">
+        <v>10</v>
       </c>
       <c r="AH25" s="30" t="s">
         <v>4</v>
@@ -3867,14 +3779,14 @@
       <c r="AK25" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="AL25" s="36" t="s">
-        <v>11</v>
+      <c r="AL25" s="34" t="s">
+        <v>7</v>
       </c>
       <c r="AU25" s="3"/>
       <c r="AV25" s="3"/>
       <c r="AW25" s="3"/>
-      <c r="AX25" s="34"/>
-      <c r="AY25" s="34"/>
+      <c r="AX25" s="33"/>
+      <c r="AY25" s="33"/>
       <c r="AZ25" s="18"/>
       <c r="BA25" s="18"/>
       <c r="BB25" s="18"/>
@@ -3920,8 +3832,8 @@
       <c r="C26" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="D26" s="37" t="s">
-        <v>9</v>
+      <c r="D26" s="27" t="s">
+        <v>1</v>
       </c>
       <c r="E26" s="30" t="s">
         <v>4</v>
@@ -3935,81 +3847,81 @@
       <c r="H26" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="I26" s="45" t="s">
+      <c r="I26" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="J26" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="J26" s="42" t="s">
+      <c r="K26" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="K26" s="41" t="s">
+      <c r="L26" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="M26" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="N26" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="O26" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="P26" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q26" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="R26" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="L26" s="31" t="s">
-        <v>5</v>
-      </c>
-      <c r="M26" s="31" t="s">
-        <v>5</v>
-      </c>
-      <c r="N26" s="31" t="s">
-        <v>5</v>
-      </c>
-      <c r="O26" s="31" t="s">
-        <v>5</v>
-      </c>
-      <c r="P26" s="40" t="s">
+      <c r="S26" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="T26" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="U26" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="V26" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="W26" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="X26" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y26" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z26" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="Q26" s="41" t="s">
+      <c r="AA26" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB26" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC26" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD26" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE26" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="AF26" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG26" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="R26" s="46" t="s">
-        <v>11</v>
-      </c>
-      <c r="S26" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="T26" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="U26" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="V26" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="W26" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="X26" s="47" t="s">
-        <v>11</v>
-      </c>
-      <c r="Y26" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z26" s="41" t="s">
-        <v>13</v>
-      </c>
-      <c r="AA26" s="31" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB26" s="31" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC26" s="31" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD26" s="31" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE26" s="40" t="s">
-        <v>12</v>
-      </c>
-      <c r="AF26" s="42" t="s">
-        <v>13</v>
-      </c>
-      <c r="AG26" s="45" t="s">
-        <v>11</v>
-      </c>
       <c r="AH26" s="30" t="s">
         <v>4</v>
       </c>
@@ -4022,14 +3934,14 @@
       <c r="AK26" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="AL26" s="38" t="s">
-        <v>9</v>
+      <c r="AL26" s="27" t="s">
+        <v>1</v>
       </c>
       <c r="AU26" s="3"/>
       <c r="AV26" s="3"/>
       <c r="AW26" s="3"/>
-      <c r="AX26" s="34"/>
-      <c r="AY26" s="34"/>
+      <c r="AX26" s="33"/>
+      <c r="AY26" s="33"/>
       <c r="AZ26" s="18"/>
       <c r="BA26" s="18"/>
       <c r="BB26" s="18"/>
@@ -4075,8 +3987,8 @@
       <c r="C27" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="D27" s="35" t="s">
-        <v>11</v>
+      <c r="D27" s="34" t="s">
+        <v>7</v>
       </c>
       <c r="E27" s="30" t="s">
         <v>4</v>
@@ -4177,13 +4089,13 @@
       <c r="AK27" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="AL27" s="36" t="s">
-        <v>11</v>
+      <c r="AL27" s="34" t="s">
+        <v>7</v>
       </c>
       <c r="AU27" s="3"/>
       <c r="AV27" s="3"/>
       <c r="AW27" s="3"/>
-      <c r="AX27" s="34"/>
+      <c r="AX27" s="33"/>
       <c r="AY27" s="18"/>
       <c r="AZ27" s="18"/>
       <c r="BA27" s="18"/>
@@ -4230,8 +4142,8 @@
       <c r="C28" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="D28" s="37" t="s">
-        <v>9</v>
+      <c r="D28" s="27" t="s">
+        <v>1</v>
       </c>
       <c r="E28" s="30" t="s">
         <v>4</v>
@@ -4332,13 +4244,13 @@
       <c r="AK28" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="AL28" s="38" t="s">
-        <v>9</v>
+      <c r="AL28" s="27" t="s">
+        <v>1</v>
       </c>
       <c r="AU28" s="3"/>
       <c r="AV28" s="3"/>
       <c r="AW28" s="3"/>
-      <c r="AX28" s="34"/>
+      <c r="AX28" s="33"/>
       <c r="AY28" s="18"/>
       <c r="AZ28" s="18"/>
       <c r="BA28" s="18"/>
@@ -4385,8 +4297,8 @@
       <c r="C29" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="D29" s="35" t="s">
-        <v>11</v>
+      <c r="D29" s="34" t="s">
+        <v>7</v>
       </c>
       <c r="E29" s="30" t="s">
         <v>4</v>
@@ -4487,13 +4399,13 @@
       <c r="AK29" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="AL29" s="36" t="s">
-        <v>11</v>
+      <c r="AL29" s="34" t="s">
+        <v>7</v>
       </c>
       <c r="AU29" s="3"/>
       <c r="AV29" s="3"/>
       <c r="AW29" s="3"/>
-      <c r="AX29" s="34"/>
+      <c r="AX29" s="33"/>
       <c r="AY29" s="18"/>
       <c r="AZ29" s="18"/>
       <c r="BA29" s="18"/>
@@ -4540,8 +4452,8 @@
       <c r="C30" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="D30" s="37" t="s">
-        <v>9</v>
+      <c r="D30" s="27" t="s">
+        <v>1</v>
       </c>
       <c r="E30" s="30" t="s">
         <v>4</v>
@@ -4642,13 +4554,13 @@
       <c r="AK30" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="AL30" s="38" t="s">
-        <v>9</v>
+      <c r="AL30" s="27" t="s">
+        <v>1</v>
       </c>
       <c r="AU30" s="3"/>
       <c r="AV30" s="3"/>
       <c r="AW30" s="3"/>
-      <c r="AX30" s="34"/>
+      <c r="AX30" s="33"/>
       <c r="AY30" s="18"/>
       <c r="AZ30" s="18"/>
       <c r="BA30" s="18"/>
@@ -4695,115 +4607,115 @@
       <c r="C31" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="D31" s="48" t="s">
-        <v>11</v>
-      </c>
-      <c r="E31" s="49" t="s">
-        <v>12</v>
-      </c>
-      <c r="F31" s="50" t="s">
-        <v>13</v>
-      </c>
-      <c r="G31" s="49" t="s">
-        <v>12</v>
-      </c>
-      <c r="H31" s="50" t="s">
-        <v>13</v>
-      </c>
-      <c r="I31" s="49" t="s">
-        <v>12</v>
-      </c>
-      <c r="J31" s="50" t="s">
-        <v>13</v>
-      </c>
-      <c r="K31" s="49" t="s">
-        <v>12</v>
-      </c>
-      <c r="L31" s="50" t="s">
-        <v>13</v>
-      </c>
-      <c r="M31" s="49" t="s">
-        <v>12</v>
-      </c>
-      <c r="N31" s="50" t="s">
-        <v>13</v>
-      </c>
-      <c r="O31" s="49" t="s">
-        <v>12</v>
-      </c>
-      <c r="P31" s="50" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q31" s="51" t="n">
+      <c r="D31" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="E31" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="F31" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="G31" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="H31" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="I31" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="J31" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="K31" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="L31" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="M31" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="N31" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="O31" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="P31" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q31" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="R31" s="52" t="n">
+      <c r="R31" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="S31" s="52" t="n">
+      <c r="S31" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="T31" s="52" t="n">
+      <c r="T31" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="U31" s="52" t="n">
+      <c r="U31" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="V31" s="52" t="n">
+      <c r="V31" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="W31" s="52" t="n">
+      <c r="W31" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="X31" s="52" t="n">
+      <c r="X31" s="45" t="n">
         <v>1</v>
       </c>
-      <c r="Y31" s="53" t="n">
+      <c r="Y31" s="46" t="n">
         <v>1</v>
       </c>
-      <c r="Z31" s="50" t="s">
-        <v>12</v>
-      </c>
-      <c r="AA31" s="50" t="s">
-        <v>13</v>
-      </c>
-      <c r="AB31" s="49" t="s">
-        <v>12</v>
-      </c>
-      <c r="AC31" s="50" t="s">
-        <v>13</v>
-      </c>
-      <c r="AD31" s="49" t="s">
-        <v>12</v>
-      </c>
-      <c r="AE31" s="50" t="s">
-        <v>13</v>
-      </c>
-      <c r="AF31" s="49" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG31" s="50" t="s">
-        <v>13</v>
-      </c>
-      <c r="AH31" s="49" t="s">
-        <v>12</v>
-      </c>
-      <c r="AI31" s="50" t="s">
-        <v>13</v>
-      </c>
-      <c r="AJ31" s="49" t="s">
-        <v>12</v>
-      </c>
-      <c r="AK31" s="50" t="s">
-        <v>13</v>
-      </c>
-      <c r="AL31" s="54" t="s">
-        <v>11</v>
+      <c r="Z31" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA31" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB31" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC31" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD31" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="AE31" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF31" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="AG31" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH31" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="AI31" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ31" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="AK31" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL31" s="34" t="s">
+        <v>7</v>
       </c>
       <c r="AU31" s="3"/>
       <c r="AV31" s="3"/>
       <c r="AW31" s="3"/>
-      <c r="AX31" s="34"/>
+      <c r="AX31" s="33"/>
       <c r="AY31" s="18"/>
       <c r="AZ31" s="18"/>
       <c r="BA31" s="18"/>
@@ -4898,7 +4810,7 @@
       <c r="T32" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="U32" s="55" t="n">
+      <c r="U32" s="47" t="n">
         <v>18</v>
       </c>
       <c r="V32" s="1" t="n">
@@ -5062,7 +4974,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5077,7 +4989,7 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5092,7 +5004,7 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5107,7 +5019,7 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5122,7 +5034,7 @@
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5137,7 +5049,7 @@
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
